--- a/templates/ERC000039/metadata_template_ERC000039.xlsx
+++ b/templates/ERC000039/metadata_template_ERC000039.xlsx
@@ -24,7 +24,7 @@
     <definedName name="hostdiseaseoutcome">'cv_sample'!$R$1:$R$3</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$V$1:$V$14</definedName>
     <definedName name="hostsex">'cv_sample'!$W$1:$W$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="644">
   <si>
     <t>alias</t>
   </si>
@@ -561,6 +561,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -724,6 +727,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2492,7 +2498,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2536,7 +2542,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2563,7 +2569,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3282,6 +3288,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3303,27 +3319,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3343,122 +3359,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3482,192 +3498,192 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -3705,241 +3721,241 @@
   <sheetData>
     <row r="1" spans="9:23">
       <c r="I1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="R1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="V1" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="W1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2" spans="9:23">
       <c r="I2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="R2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="V2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="W2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="3" spans="9:23">
       <c r="I3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="R3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="V3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="W3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" spans="9:23">
       <c r="K4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="V4" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="W4" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="5" spans="9:23">
       <c r="K5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="V5" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="W5" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="9:23">
       <c r="K6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="V6" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="W6" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="7" spans="9:23">
       <c r="K7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q7" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="V7" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="W7" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8" spans="9:23">
       <c r="K8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V8" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="W8" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="9:23">
       <c r="K9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="V9" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="W9" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" spans="9:23">
       <c r="K10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q10" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="V10" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="W10" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" spans="9:23">
       <c r="K11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="V11" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="W11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" spans="9:23">
       <c r="K12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="V12" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="W12" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="13" spans="9:23">
       <c r="K13" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="V13" t="s">
+        <v>601</v>
+      </c>
+      <c r="W13" t="s">
         <v>599</v>
-      </c>
-      <c r="W13" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="14" spans="9:23">
       <c r="K14" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V14" t="s">
+        <v>602</v>
+      </c>
+      <c r="W14" t="s">
         <v>600</v>
-      </c>
-      <c r="W14" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="15" spans="9:23">
       <c r="K15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q15" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="W15" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="16" spans="9:23">
       <c r="K16" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q16" t="s">
         <v>300</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>298</v>
       </c>
       <c r="W16" t="s">
         <v>116</v>
@@ -3947,2141 +3963,2141 @@
     </row>
     <row r="17" spans="11:23">
       <c r="K17" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q17" t="s">
         <v>301</v>
       </c>
-      <c r="Q17" t="s">
-        <v>299</v>
-      </c>
       <c r="W17" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="18" spans="11:23">
       <c r="K18" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q18" t="s">
         <v>302</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="19" spans="11:23">
       <c r="K19" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q19" t="s">
         <v>303</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="20" spans="11:23">
       <c r="K20" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q20" t="s">
         <v>304</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="21" spans="11:23">
       <c r="K21" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q21" t="s">
         <v>305</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="22" spans="11:23">
       <c r="K22" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q22" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="23" spans="11:23">
       <c r="K23" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q23" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="11:23">
       <c r="K24" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q24" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="11:23">
       <c r="K25" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="11:23">
       <c r="K26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q26" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="11:23">
       <c r="K27" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q27" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="11:23">
       <c r="K28" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q28" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="11:23">
       <c r="K29" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q29" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="11:23">
       <c r="K30" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q30" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="11:23">
       <c r="K31" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q31" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="11:23">
       <c r="K32" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q32" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="11:17">
       <c r="K33" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q33" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="34" spans="11:17">
       <c r="K34" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="11:17">
       <c r="K35" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q35" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="11:17">
       <c r="K36" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q36" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="11:17">
       <c r="K37" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="11:17">
       <c r="K38" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q38" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="11:17">
       <c r="K39" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" spans="11:17">
       <c r="K40" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q40" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="11:17">
       <c r="K41" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q41" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" spans="11:17">
       <c r="K42" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q42" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="11:17">
       <c r="K43" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q43" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="11:17">
       <c r="K44" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q44" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="11:17">
       <c r="K45" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q45" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" spans="11:17">
       <c r="K46" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q46" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="11:17">
       <c r="K47" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q47" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="11:17">
       <c r="K48" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q48" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" spans="11:17">
       <c r="K49" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q49" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="50" spans="11:17">
       <c r="K50" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q50" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51" spans="11:17">
       <c r="K51" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q51" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="11:17">
       <c r="K52" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q52" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="11:17">
       <c r="K53" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q53" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54" spans="11:17">
       <c r="K54" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q54" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" spans="11:17">
       <c r="K55" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q55" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="11:17">
       <c r="K56" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q56" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="11:17">
       <c r="K57" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q57" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="11:17">
       <c r="K58" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q58" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="11:17">
       <c r="K59" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q59" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="11:17">
       <c r="K60" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q60" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="61" spans="11:17">
       <c r="K61" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q61" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" spans="11:17">
       <c r="K62" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q62" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="11:17">
       <c r="K63" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q63" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="64" spans="11:17">
       <c r="K64" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q64" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="11:17">
       <c r="K65" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q65" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="66" spans="11:17">
       <c r="K66" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q66" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="67" spans="11:17">
       <c r="K67" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q67" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="68" spans="11:17">
       <c r="K68" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q68" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="11:17">
       <c r="K69" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q69" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="11:17">
       <c r="K70" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q70" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="11:17">
       <c r="K71" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q71" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="11:17">
       <c r="K72" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q72" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="73" spans="11:17">
       <c r="K73" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q73" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="11:17">
       <c r="K74" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q74" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="75" spans="11:17">
       <c r="K75" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q75" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76" spans="11:17">
       <c r="K76" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q76" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" spans="11:17">
       <c r="K77" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q77" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="78" spans="11:17">
       <c r="K78" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q78" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="79" spans="11:17">
       <c r="K79" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q79" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80" spans="11:17">
       <c r="K80" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q80" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="11:17">
       <c r="K81" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q81" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="82" spans="11:17">
       <c r="K82" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q82" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="83" spans="11:17">
       <c r="K83" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q83" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" spans="11:17">
       <c r="K84" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q84" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="11:17">
       <c r="K85" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q85" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="11:17">
       <c r="K86" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q86" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" spans="11:17">
       <c r="K87" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q87" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" spans="11:17">
       <c r="K88" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q88" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="89" spans="11:17">
       <c r="K89" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q89" t="s">
         <v>373</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="90" spans="11:17">
       <c r="K90" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q90" t="s">
         <v>374</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="91" spans="11:17">
       <c r="K91" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q91" t="s">
         <v>375</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="92" spans="11:17">
       <c r="K92" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q92" t="s">
         <v>376</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="93" spans="11:17">
       <c r="K93" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q93" t="s">
         <v>377</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="94" spans="11:17">
       <c r="K94" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q94" t="s">
         <v>378</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="95" spans="11:17">
       <c r="K95" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q95" t="s">
         <v>379</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="96" spans="11:17">
       <c r="K96" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q96" t="s">
         <v>380</v>
-      </c>
-      <c r="Q96" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="97" spans="11:17">
       <c r="K97" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q97" t="s">
         <v>381</v>
-      </c>
-      <c r="Q97" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="98" spans="11:17">
       <c r="K98" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q98" t="s">
         <v>382</v>
-      </c>
-      <c r="Q98" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="99" spans="11:17">
       <c r="K99" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q99" t="s">
         <v>383</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="100" spans="11:17">
       <c r="K100" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q100" t="s">
         <v>384</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="101" spans="11:17">
       <c r="K101" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q101" t="s">
         <v>385</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="102" spans="11:17">
       <c r="K102" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q102" t="s">
         <v>386</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="103" spans="11:17">
       <c r="K103" t="s">
+        <v>389</v>
+      </c>
+      <c r="Q103" t="s">
         <v>387</v>
-      </c>
-      <c r="Q103" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="104" spans="11:17">
       <c r="K104" t="s">
+        <v>390</v>
+      </c>
+      <c r="Q104" t="s">
         <v>388</v>
-      </c>
-      <c r="Q104" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="105" spans="11:17">
       <c r="K105" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q105" t="s">
         <v>389</v>
-      </c>
-      <c r="Q105" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="106" spans="11:17">
       <c r="K106" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q106" t="s">
         <v>390</v>
-      </c>
-      <c r="Q106" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="107" spans="11:17">
       <c r="K107" t="s">
+        <v>393</v>
+      </c>
+      <c r="Q107" t="s">
         <v>391</v>
-      </c>
-      <c r="Q107" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="108" spans="11:17">
       <c r="K108" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q108" t="s">
         <v>392</v>
-      </c>
-      <c r="Q108" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="109" spans="11:17">
       <c r="K109" t="s">
+        <v>395</v>
+      </c>
+      <c r="Q109" t="s">
         <v>393</v>
-      </c>
-      <c r="Q109" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="110" spans="11:17">
       <c r="K110" t="s">
+        <v>396</v>
+      </c>
+      <c r="Q110" t="s">
         <v>394</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="111" spans="11:17">
       <c r="K111" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q111" t="s">
         <v>395</v>
-      </c>
-      <c r="Q111" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="112" spans="11:17">
       <c r="K112" t="s">
+        <v>398</v>
+      </c>
+      <c r="Q112" t="s">
         <v>396</v>
-      </c>
-      <c r="Q112" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="113" spans="11:17">
       <c r="K113" t="s">
+        <v>399</v>
+      </c>
+      <c r="Q113" t="s">
         <v>397</v>
-      </c>
-      <c r="Q113" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="114" spans="11:17">
       <c r="K114" t="s">
+        <v>400</v>
+      </c>
+      <c r="Q114" t="s">
         <v>398</v>
-      </c>
-      <c r="Q114" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="115" spans="11:17">
       <c r="K115" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q115" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="116" spans="11:17">
       <c r="K116" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q116" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="11:17">
       <c r="K117" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q117" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="11:17">
       <c r="K118" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q118" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="11:17">
       <c r="K119" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q119" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="120" spans="11:17">
       <c r="K120" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q120" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="11:17">
       <c r="K121" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q121" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="122" spans="11:17">
       <c r="K122" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q122" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="123" spans="11:17">
       <c r="K123" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q123" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="124" spans="11:17">
       <c r="K124" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q124" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="125" spans="11:17">
       <c r="K125" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q125" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="126" spans="11:17">
       <c r="K126" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q126" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="127" spans="11:17">
       <c r="K127" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q127" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="128" spans="11:17">
       <c r="K128" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q128" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="129" spans="11:17">
       <c r="K129" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q129" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="130" spans="11:17">
       <c r="K130" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q130" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="131" spans="11:17">
       <c r="K131" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q131" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="132" spans="11:17">
       <c r="K132" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q132" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="133" spans="11:17">
       <c r="K133" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q133" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="134" spans="11:17">
       <c r="K134" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q134" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="135" spans="11:17">
       <c r="K135" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q135" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="11:17">
       <c r="K136" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q136" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="137" spans="11:17">
       <c r="K137" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q137" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="11:17">
       <c r="K138" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q138" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="139" spans="11:17">
       <c r="K139" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q139" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="11:17">
       <c r="K140" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q140" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="141" spans="11:17">
       <c r="K141" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q141" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="142" spans="11:17">
       <c r="K142" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Q142" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="143" spans="11:17">
       <c r="K143" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q143" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="144" spans="11:17">
       <c r="K144" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q144" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="145" spans="11:17">
       <c r="K145" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q145" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="146" spans="11:17">
       <c r="K146" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Q146" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="147" spans="11:17">
       <c r="K147" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q147" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="148" spans="11:17">
       <c r="K148" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q148" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="149" spans="11:17">
       <c r="K149" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q149" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="150" spans="11:17">
       <c r="K150" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q150" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="151" spans="11:17">
       <c r="K151" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q151" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="152" spans="11:17">
       <c r="K152" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q152" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="153" spans="11:17">
       <c r="K153" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q153" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="154" spans="11:17">
       <c r="K154" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q154" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="155" spans="11:17">
       <c r="K155" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q155" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="156" spans="11:17">
       <c r="K156" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Q156" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="157" spans="11:17">
       <c r="K157" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q157" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="158" spans="11:17">
       <c r="K158" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q158" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="159" spans="11:17">
       <c r="K159" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="Q159" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="160" spans="11:17">
       <c r="K160" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q160" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="161" spans="11:17">
       <c r="K161" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q161" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="162" spans="11:17">
       <c r="K162" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Q162" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="163" spans="11:17">
       <c r="K163" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q163" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="164" spans="11:17">
       <c r="K164" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Q164" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="165" spans="11:17">
       <c r="K165" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q165" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="166" spans="11:17">
       <c r="K166" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Q166" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="167" spans="11:17">
       <c r="K167" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q167" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="168" spans="11:17">
       <c r="K168" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Q168" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="169" spans="11:17">
       <c r="K169" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q169" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="170" spans="11:17">
       <c r="K170" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Q170" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="171" spans="11:17">
       <c r="K171" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Q171" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="172" spans="11:17">
       <c r="K172" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Q172" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="173" spans="11:17">
       <c r="K173" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q173" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="174" spans="11:17">
       <c r="K174" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="Q174" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="175" spans="11:17">
       <c r="K175" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Q175" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="176" spans="11:17">
       <c r="K176" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Q176" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="177" spans="11:17">
       <c r="K177" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Q177" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="178" spans="11:17">
       <c r="K178" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="Q178" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="179" spans="11:17">
       <c r="K179" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="Q179" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="180" spans="11:17">
       <c r="K180" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Q180" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="181" spans="11:17">
       <c r="K181" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="Q181" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="182" spans="11:17">
       <c r="K182" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="Q182" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="183" spans="11:17">
       <c r="K183" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="Q183" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="184" spans="11:17">
       <c r="K184" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Q184" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="185" spans="11:17">
       <c r="K185" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="Q185" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="186" spans="11:17">
       <c r="K186" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Q186" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="187" spans="11:17">
       <c r="K187" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Q187" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="188" spans="11:17">
       <c r="K188" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="Q188" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="189" spans="11:17">
       <c r="K189" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q189" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="190" spans="11:17">
       <c r="K190" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="Q190" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="191" spans="11:17">
       <c r="K191" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="Q191" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="192" spans="11:17">
       <c r="K192" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="Q192" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="193" spans="11:17">
       <c r="K193" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="Q193" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="194" spans="11:17">
       <c r="K194" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="Q194" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="195" spans="11:17">
       <c r="K195" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Q195" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="196" spans="11:17">
       <c r="K196" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Q196" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="197" spans="11:17">
       <c r="K197" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="Q197" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="198" spans="11:17">
       <c r="K198" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="Q198" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="199" spans="11:17">
       <c r="K199" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Q199" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="200" spans="11:17">
       <c r="K200" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="Q200" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="201" spans="11:17">
       <c r="K201" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="Q201" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="202" spans="11:17">
       <c r="K202" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="Q202" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="203" spans="11:17">
       <c r="K203" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="Q203" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="204" spans="11:17">
       <c r="K204" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="Q204" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="205" spans="11:17">
       <c r="K205" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="Q205" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="206" spans="11:17">
       <c r="K206" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="Q206" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="207" spans="11:17">
       <c r="K207" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Q207" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="208" spans="11:17">
       <c r="K208" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q208" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="209" spans="11:17">
       <c r="K209" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="Q209" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="210" spans="11:17">
       <c r="K210" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Q210" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="211" spans="11:17">
       <c r="K211" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Q211" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="212" spans="11:17">
       <c r="K212" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Q212" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="213" spans="11:17">
       <c r="K213" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="Q213" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="214" spans="11:17">
       <c r="K214" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="Q214" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="215" spans="11:17">
       <c r="K215" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="Q215" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="216" spans="11:17">
       <c r="K216" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="Q216" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="217" spans="11:17">
       <c r="K217" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="Q217" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="218" spans="11:17">
       <c r="K218" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="Q218" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="219" spans="11:17">
       <c r="K219" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Q219" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="220" spans="11:17">
       <c r="K220" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="Q220" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="221" spans="11:17">
       <c r="K221" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="Q221" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="222" spans="11:17">
       <c r="K222" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="Q222" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="223" spans="11:17">
       <c r="K223" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Q223" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="224" spans="11:17">
       <c r="K224" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="Q224" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="225" spans="11:17">
       <c r="K225" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="Q225" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="226" spans="11:17">
       <c r="K226" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="Q226" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="227" spans="11:17">
       <c r="K227" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="Q227" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="228" spans="11:17">
       <c r="K228" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="Q228" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="229" spans="11:17">
       <c r="K229" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="Q229" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="230" spans="11:17">
       <c r="K230" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="Q230" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="231" spans="11:17">
       <c r="K231" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="Q231" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="232" spans="11:17">
       <c r="K232" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="Q232" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="233" spans="11:17">
       <c r="K233" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Q233" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="234" spans="11:17">
       <c r="K234" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Q234" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="235" spans="11:17">
       <c r="K235" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q235" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="236" spans="11:17">
       <c r="K236" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="Q236" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="237" spans="11:17">
       <c r="K237" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="Q237" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="238" spans="11:17">
       <c r="K238" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="Q238" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="239" spans="11:17">
       <c r="K239" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="Q239" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="240" spans="11:17">
       <c r="K240" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Q240" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="241" spans="11:17">
       <c r="K241" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="Q241" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="242" spans="11:17">
       <c r="K242" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="Q242" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="243" spans="11:17">
       <c r="K243" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="Q243" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="244" spans="11:17">
       <c r="K244" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="Q244" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="245" spans="11:17">
       <c r="K245" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="Q245" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="246" spans="11:17">
       <c r="K246" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="Q246" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="247" spans="11:17">
       <c r="K247" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="Q247" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="248" spans="11:17">
       <c r="K248" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="Q248" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="249" spans="11:17">
       <c r="K249" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="Q249" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="250" spans="11:17">
       <c r="K250" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="Q250" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="251" spans="11:17">
       <c r="K251" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="Q251" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="252" spans="11:17">
       <c r="K252" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="Q252" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="253" spans="11:17">
       <c r="K253" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Q253" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="254" spans="11:17">
       <c r="K254" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="Q254" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="255" spans="11:17">
       <c r="K255" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="Q255" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="256" spans="11:17">
       <c r="K256" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="Q256" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="257" spans="11:17">
       <c r="K257" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Q257" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="258" spans="11:17">
       <c r="K258" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="Q258" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="259" spans="11:17">
       <c r="K259" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="Q259" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="260" spans="11:17">
       <c r="K260" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="Q260" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="261" spans="11:17">
       <c r="K261" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="Q261" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="262" spans="11:17">
       <c r="K262" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="Q262" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="263" spans="11:17">
       <c r="K263" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="Q263" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="264" spans="11:17">
       <c r="K264" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="Q264" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="265" spans="11:17">
       <c r="K265" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="Q265" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="266" spans="11:17">
       <c r="K266" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="Q266" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="267" spans="11:17">
       <c r="K267" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="Q267" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="268" spans="11:17">
       <c r="K268" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="Q268" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="269" spans="11:17">
       <c r="K269" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Q269" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="270" spans="11:17">
       <c r="K270" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="Q270" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="271" spans="11:17">
       <c r="K271" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="Q271" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="272" spans="11:17">
       <c r="K272" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="Q272" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="273" spans="11:17">
       <c r="K273" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="Q273" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="274" spans="11:17">
       <c r="Q274" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="275" spans="11:17">
       <c r="Q275" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="276" spans="11:17">
       <c r="Q276" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="277" spans="11:17">
       <c r="Q277" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="278" spans="11:17">
       <c r="Q278" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="279" spans="11:17">
       <c r="Q279" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="280" spans="11:17">
       <c r="Q280" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="281" spans="11:17">
       <c r="Q281" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="282" spans="11:17">
       <c r="Q282" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="283" spans="11:17">
       <c r="Q283" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="284" spans="11:17">
       <c r="Q284" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="285" spans="11:17">
       <c r="Q285" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="286" spans="11:17">
       <c r="Q286" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="287" spans="11:17">
       <c r="Q287" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="288" spans="11:17">
       <c r="Q288" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="289" spans="17:17">
       <c r="Q289" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000039/metadata_template_ERC000039.xlsx
+++ b/templates/ERC000039/metadata_template_ERC000039.xlsx
@@ -20,11 +20,11 @@
     <definedName name="clinicalsetting">'cv_sample'!$J$1:$J$2</definedName>
     <definedName name="countryoftravel">'cv_sample'!$K$1:$K$273</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$Q$1:$Q$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$Q$1:$Q$294</definedName>
     <definedName name="hostdiseaseoutcome">'cv_sample'!$R$1:$R$3</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$V$1:$V$14</definedName>
     <definedName name="hostsex">'cv_sample'!$W$1:$W$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="647">
   <si>
     <t>alias</t>
   </si>
@@ -561,6 +561,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -852,19 +855,19 @@
     <t>(Mandatory) If the sample was obtained from an organism in a specific developmental stage, it is specified with this qualifier</t>
   </si>
   <si>
-    <t>known pathogenicity</t>
+    <t>known_pathogenicity</t>
   </si>
   <si>
     <t>(Recommended) To what is the entity pathogenic, for instance plant, fungi, bacteria</t>
   </si>
   <si>
-    <t>sample storage conditions</t>
+    <t>sample_storage_conditions</t>
   </si>
   <si>
     <t>(Optional) Conditions at which sample was stored, usually storage temperature, duration and location. in soil context: explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other).</t>
   </si>
   <si>
-    <t>subject exposure</t>
+    <t>subject_exposure</t>
   </si>
   <si>
     <t>(Optional) Exposure of the subject to infected human or animals, such as poultry, wild bird or swine. if multiple exposures are applicable, please state them separated by semicolon. example: poultry; wild bird</t>
@@ -879,7 +882,7 @@
     <t>travel-related</t>
   </si>
   <si>
-    <t>travel-relation</t>
+    <t>travelrelation</t>
   </si>
   <si>
     <t>(Optional) Designates the relation of the main diagnosis to the patient's travel.</t>
@@ -891,7 +894,7 @@
     <t>during travel</t>
   </si>
   <si>
-    <t>clinical setting</t>
+    <t>clinical_setting</t>
   </si>
   <si>
     <t>(Optional) The timing of the clinic visit in relation to travel.</t>
@@ -1716,40 +1719,40 @@
     <t>Zimbabwe</t>
   </si>
   <si>
-    <t>country of travel</t>
+    <t>country_of_travel</t>
   </si>
   <si>
     <t>(Optional) The name of the country of patient's travel.</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
   </si>
   <si>
-    <t>geographic location (latitude)</t>
+    <t>geographic_location_latitude</t>
   </si>
   <si>
     <t>(Recommended) The geographical origin of the sample as defined by latitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (longitude)</t>
+    <t>geographic_location_longitude</t>
   </si>
   <si>
     <t>(Recommended) The geographical origin of the sample as defined by longitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (region and locality)</t>
+    <t>geographic_location_region_and_locality</t>
   </si>
   <si>
     <t>(Optional) The geographical origin of the sample as defined by the specific region name followed by the locality name.</t>
   </si>
   <si>
-    <t>subject exposure duration</t>
-  </si>
-  <si>
-    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: year)</t>
+    <t>subject_exposure_duration</t>
+  </si>
+  <si>
+    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: day)</t>
   </si>
   <si>
     <t>Arctic Ocean</t>
@@ -1770,7 +1773,7 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>East Timor</t>
+    <t>Eswatini</t>
   </si>
   <si>
     <t>Falkland Islands (Islas Malvinas)</t>
@@ -1782,12 +1785,21 @@
     <t>Kerguelen Archipelago</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Mediterranean Sea</t>
   </si>
   <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
     <t>Myanmar</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1845,7 +1857,7 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
@@ -1860,25 +1872,25 @@
     <t>recovered with sequelae</t>
   </si>
   <si>
-    <t>host disease outcome</t>
+    <t>host_disease_outcome</t>
   </si>
   <si>
     <t>(Recommended) Disease outcome in the host.</t>
   </si>
   <si>
-    <t>host common name</t>
+    <t>host_common_name</t>
   </si>
   <si>
     <t>(Recommended) Common name of the host, e.g. human</t>
   </si>
   <si>
-    <t>host subject id</t>
+    <t>host_subject_id</t>
   </si>
   <si>
     <t>(Recommended) A unique identifier by which each subject can be referred to, de-identified, e.g. #131</t>
   </si>
   <si>
-    <t>host age</t>
+    <t>host_age</t>
   </si>
   <si>
     <t>(Recommended) Age of host at the time of sampling; relevant scale depends on species and study, e.g. could be seconds for amoebae or centuries for trees (Units: years)</t>
@@ -1890,7 +1902,7 @@
     <t>healthy</t>
   </si>
   <si>
-    <t>host health state</t>
+    <t>host_health_state</t>
   </si>
   <si>
     <t>(Recommended) Health status of the host at the time of sample collection.</t>
@@ -1908,25 +1920,25 @@
     <t>neuter</t>
   </si>
   <si>
-    <t>host sex</t>
+    <t>host_sex</t>
   </si>
   <si>
     <t>(Recommended) Gender or sex of the host.</t>
   </si>
   <si>
-    <t>host scientific name</t>
+    <t>host_scientific_name</t>
   </si>
   <si>
     <t>(Recommended) Scientific name of the natural (as opposed to laboratory) host to the organism from which sample was obtained.</t>
   </si>
   <si>
-    <t>collector name</t>
+    <t>collector_name</t>
   </si>
   <si>
     <t>(Mandatory) Name of the person who collected the specimen. example: john smith</t>
   </si>
   <si>
-    <t>collecting institution</t>
+    <t>collecting_institution</t>
   </si>
   <si>
     <t>(Mandatory) Name of the institution to which the person collecting the specimen belongs. format: institute name, institute address</t>
@@ -1944,13 +1956,13 @@
     <t>(Recommended) Name of the strain from which the sample was obtained.</t>
   </si>
   <si>
-    <t>isolation source host-associated</t>
+    <t>isolation_source_hostassociated</t>
   </si>
   <si>
     <t>(Recommended) Name of host tissue or organ sampled for analysis. example: tracheal tissue</t>
   </si>
   <si>
-    <t>diagnostic method</t>
+    <t>diagnostic_method</t>
   </si>
   <si>
     <t>(Recommended) The method or procedure (imaging, genetic or other) performed to determine or confirm the presence of disease in an individual. examples: microscopy, immunofluorescence, pcr, rapid tests, etc.</t>
@@ -1962,7 +1974,7 @@
     <t>(Recommended) Name or code for genotype of organism</t>
   </si>
   <si>
-    <t>isolation source non-host-associated</t>
+    <t>isolation_source_nonhostassociated</t>
   </si>
   <si>
     <t>(Recommended) Describes the physical, environmental and/or local geographical source of the biological sample from which the sample was derived. example: soil</t>
@@ -2495,7 +2507,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2539,7 +2551,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2566,7 +2578,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3290,6 +3302,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3311,27 +3328,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3351,122 +3368,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3490,192 +3507,192 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>
@@ -3708,246 +3725,246 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="I1:W289"/>
+  <dimension ref="I1:W294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="9:23">
       <c r="I1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R1" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="V1" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="W1" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" spans="9:23">
       <c r="I2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="R2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="V2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="W2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="3" spans="9:23">
       <c r="I3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="R3" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="V3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="W3" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
     </row>
     <row r="4" spans="9:23">
       <c r="K4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V4" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="W4" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" spans="9:23">
       <c r="K5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="V5" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="W5" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="6" spans="9:23">
       <c r="K6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="V6" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="W6" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" spans="9:23">
       <c r="K7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="V7" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="W7" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8" spans="9:23">
       <c r="K8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="V8" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="W8" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="9:23">
       <c r="K9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="V9" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="W9" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="9:23">
       <c r="K10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q10" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="V10" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="W10" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="9:23">
       <c r="K11" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q11" t="s">
         <v>296</v>
       </c>
-      <c r="Q11" t="s">
-        <v>295</v>
-      </c>
       <c r="V11" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="W11" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" spans="9:23">
       <c r="K12" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q12" t="s">
         <v>297</v>
       </c>
-      <c r="Q12" t="s">
-        <v>296</v>
-      </c>
       <c r="V12" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="W12" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="13" spans="9:23">
       <c r="K13" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q13" t="s">
         <v>298</v>
       </c>
-      <c r="Q13" t="s">
-        <v>297</v>
-      </c>
       <c r="V13" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="W13" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" spans="9:23">
       <c r="K14" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q14" t="s">
         <v>299</v>
       </c>
-      <c r="Q14" t="s">
-        <v>298</v>
-      </c>
       <c r="V14" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="W14" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" spans="9:23">
       <c r="K15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q15" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="W15" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16" spans="9:23">
       <c r="K16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="W16" t="s">
         <v>116</v>
@@ -3955,1050 +3972,1050 @@
     </row>
     <row r="17" spans="11:23">
       <c r="K17" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="W17" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="18" spans="11:23">
       <c r="K18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q18" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="11:23">
       <c r="K19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="11:23">
       <c r="K20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q20" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="11:23">
       <c r="K21" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q21" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="11:23">
       <c r="K22" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q22" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="23" spans="11:23">
       <c r="K23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" spans="11:23">
       <c r="K24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q24" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="25" spans="11:23">
       <c r="K25" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q25" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26" spans="11:23">
       <c r="K26" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="11:23">
       <c r="K27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q27" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="11:23">
       <c r="K28" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q28" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="11:23">
       <c r="K29" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q29" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="11:23">
       <c r="K30" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q30" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="11:23">
       <c r="K31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="11:23">
       <c r="K32" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q32" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="11:17">
       <c r="K33" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q33" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="34" spans="11:17">
       <c r="K34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="11:17">
       <c r="K35" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q35" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="11:17">
       <c r="K36" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q36" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" spans="11:17">
       <c r="K37" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q37" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="11:17">
       <c r="K38" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q38" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="11:17">
       <c r="K39" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q39" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" spans="11:17">
       <c r="K40" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q40" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="11:17">
       <c r="K41" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q41" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" spans="11:17">
       <c r="K42" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q42" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="11:17">
       <c r="K43" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q43" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" spans="11:17">
       <c r="K44" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q44" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="11:17">
       <c r="K45" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q45" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" spans="11:17">
       <c r="K46" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q46" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="47" spans="11:17">
       <c r="K47" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q47" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="11:17">
       <c r="K48" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q48" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" spans="11:17">
       <c r="K49" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q49" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="50" spans="11:17">
       <c r="K50" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q50" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="51" spans="11:17">
       <c r="K51" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q51" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52" spans="11:17">
       <c r="K52" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q52" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="53" spans="11:17">
       <c r="K53" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q53" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="54" spans="11:17">
       <c r="K54" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q54" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="55" spans="11:17">
       <c r="K55" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q55" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="11:17">
       <c r="K56" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q56" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="11:17">
       <c r="K57" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q57" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="11:17">
       <c r="K58" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q58" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="59" spans="11:17">
       <c r="K59" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q59" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="11:17">
       <c r="K60" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q60" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="61" spans="11:17">
       <c r="K61" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q61" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" spans="11:17">
       <c r="K62" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q62" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63" spans="11:17">
       <c r="K63" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q63" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="64" spans="11:17">
       <c r="K64" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q64" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="65" spans="11:17">
       <c r="K65" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q65" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="66" spans="11:17">
       <c r="K66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q66" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="67" spans="11:17">
       <c r="K67" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q67" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="68" spans="11:17">
       <c r="K68" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q68" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="69" spans="11:17">
       <c r="K69" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q69" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="70" spans="11:17">
       <c r="K70" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q70" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="11:17">
       <c r="K71" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q71" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="72" spans="11:17">
       <c r="K72" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q72" t="s">
-        <v>577</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="11:17">
       <c r="K73" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q73" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="74" spans="11:17">
       <c r="K74" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q74" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="75" spans="11:17">
       <c r="K75" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q75" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="76" spans="11:17">
       <c r="K76" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q76" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="77" spans="11:17">
       <c r="K77" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q77" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="78" spans="11:17">
       <c r="K78" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q78" t="s">
-        <v>358</v>
+        <v>578</v>
       </c>
     </row>
     <row r="79" spans="11:17">
       <c r="K79" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q79" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="80" spans="11:17">
       <c r="K80" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q80" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="11:17">
       <c r="K81" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q81" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="82" spans="11:17">
       <c r="K82" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q82" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="83" spans="11:17">
       <c r="K83" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q83" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="84" spans="11:17">
       <c r="K84" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q84" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" spans="11:17">
       <c r="K85" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q85" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="86" spans="11:17">
       <c r="K86" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q86" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="87" spans="11:17">
       <c r="K87" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q87" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" spans="11:17">
       <c r="K88" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q88" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="89" spans="11:17">
       <c r="K89" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q89" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="90" spans="11:17">
       <c r="K90" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q90" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="91" spans="11:17">
       <c r="K91" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q91" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="92" spans="11:17">
       <c r="K92" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q92" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="93" spans="11:17">
       <c r="K93" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q93" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="94" spans="11:17">
       <c r="K94" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q94" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="95" spans="11:17">
       <c r="K95" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q95" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="96" spans="11:17">
       <c r="K96" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q96" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="97" spans="11:17">
       <c r="K97" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q97" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="98" spans="11:17">
       <c r="K98" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q98" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="99" spans="11:17">
       <c r="K99" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q99" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="100" spans="11:17">
       <c r="K100" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q100" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="101" spans="11:17">
       <c r="K101" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q101" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="102" spans="11:17">
       <c r="K102" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q102" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="103" spans="11:17">
       <c r="K103" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q103" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="104" spans="11:17">
       <c r="K104" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q104" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="105" spans="11:17">
       <c r="K105" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q105" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="106" spans="11:17">
       <c r="K106" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q106" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="107" spans="11:17">
       <c r="K107" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q107" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="108" spans="11:17">
       <c r="K108" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q108" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="109" spans="11:17">
       <c r="K109" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q109" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="110" spans="11:17">
       <c r="K110" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q110" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="111" spans="11:17">
       <c r="K111" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q111" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="112" spans="11:17">
       <c r="K112" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q112" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="113" spans="11:17">
       <c r="K113" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q113" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="114" spans="11:17">
       <c r="K114" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q114" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="115" spans="11:17">
       <c r="K115" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q115" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="116" spans="11:17">
       <c r="K116" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q116" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="11:17">
       <c r="K117" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q117" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="11:17">
       <c r="K118" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q118" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="11:17">
       <c r="K119" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q119" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="120" spans="11:17">
       <c r="K120" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q120" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="11:17">
       <c r="K121" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q121" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="122" spans="11:17">
       <c r="K122" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q122" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="123" spans="11:17">
       <c r="K123" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q123" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="124" spans="11:17">
       <c r="K124" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q124" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="125" spans="11:17">
       <c r="K125" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q125" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="126" spans="11:17">
       <c r="K126" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q126" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="127" spans="11:17">
       <c r="K127" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q127" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="128" spans="11:17">
       <c r="K128" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q128" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="129" spans="11:17">
       <c r="K129" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q129" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="130" spans="11:17">
       <c r="K130" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q130" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="131" spans="11:17">
       <c r="K131" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q131" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="132" spans="11:17">
       <c r="K132" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q132" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="133" spans="11:17">
       <c r="K133" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q133" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="134" spans="11:17">
       <c r="K134" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q134" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="135" spans="11:17">
       <c r="K135" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q135" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="136" spans="11:17">
       <c r="K136" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q136" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="137" spans="11:17">
       <c r="K137" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q137" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="138" spans="11:17">
       <c r="K138" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q138" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="139" spans="11:17">
       <c r="K139" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q139" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="11:17">
       <c r="K140" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q140" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="141" spans="11:17">
       <c r="K141" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q141" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="142" spans="11:17">
       <c r="K142" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q142" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="143" spans="11:17">
       <c r="K143" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q143" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="144" spans="11:17">
       <c r="K144" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q144" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="145" spans="11:17">
       <c r="K145" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q145" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="146" spans="11:17">
       <c r="K146" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q146" t="s">
-        <v>428</v>
+        <v>582</v>
       </c>
     </row>
     <row r="147" spans="11:17">
       <c r="K147" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q147" t="s">
         <v>429</v>
@@ -5006,7 +5023,7 @@
     </row>
     <row r="148" spans="11:17">
       <c r="K148" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q148" t="s">
         <v>430</v>
@@ -5014,7 +5031,7 @@
     </row>
     <row r="149" spans="11:17">
       <c r="K149" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q149" t="s">
         <v>431</v>
@@ -5022,311 +5039,311 @@
     </row>
     <row r="150" spans="11:17">
       <c r="K150" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q150" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="151" spans="11:17">
       <c r="K151" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q151" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="152" spans="11:17">
       <c r="K152" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q152" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="153" spans="11:17">
       <c r="K153" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q153" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="154" spans="11:17">
       <c r="K154" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q154" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="155" spans="11:17">
       <c r="K155" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q155" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="156" spans="11:17">
       <c r="K156" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q156" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="157" spans="11:17">
       <c r="K157" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q157" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="158" spans="11:17">
       <c r="K158" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q158" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="159" spans="11:17">
       <c r="K159" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q159" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="160" spans="11:17">
       <c r="K160" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q160" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="161" spans="11:17">
       <c r="K161" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q161" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="162" spans="11:17">
       <c r="K162" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q162" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="163" spans="11:17">
       <c r="K163" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q163" t="s">
-        <v>444</v>
+        <v>584</v>
       </c>
     </row>
     <row r="164" spans="11:17">
       <c r="K164" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q164" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="165" spans="11:17">
       <c r="K165" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q165" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="166" spans="11:17">
       <c r="K166" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q166" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="167" spans="11:17">
       <c r="K167" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q167" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="168" spans="11:17">
       <c r="K168" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q168" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="169" spans="11:17">
       <c r="K169" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q169" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="170" spans="11:17">
       <c r="K170" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q170" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="171" spans="11:17">
       <c r="K171" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q171" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="172" spans="11:17">
       <c r="K172" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q172" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="173" spans="11:17">
       <c r="K173" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q173" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="174" spans="11:17">
       <c r="K174" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q174" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="175" spans="11:17">
       <c r="K175" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q175" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="176" spans="11:17">
       <c r="K176" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Q176" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="177" spans="11:17">
       <c r="K177" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q177" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="178" spans="11:17">
       <c r="K178" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q178" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="179" spans="11:17">
       <c r="K179" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q179" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="180" spans="11:17">
       <c r="K180" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q180" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="181" spans="11:17">
       <c r="K181" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q181" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="182" spans="11:17">
       <c r="K182" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q182" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="183" spans="11:17">
       <c r="K183" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q183" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="184" spans="11:17">
       <c r="K184" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Q184" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="185" spans="11:17">
       <c r="K185" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Q185" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="186" spans="11:17">
       <c r="K186" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q186" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="187" spans="11:17">
       <c r="K187" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q187" t="s">
-        <v>467</v>
+        <v>587</v>
       </c>
     </row>
     <row r="188" spans="11:17">
       <c r="K188" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q188" t="s">
         <v>468</v>
@@ -5334,7 +5351,7 @@
     </row>
     <row r="189" spans="11:17">
       <c r="K189" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q189" t="s">
         <v>469</v>
@@ -5342,23 +5359,23 @@
     </row>
     <row r="190" spans="11:17">
       <c r="K190" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q190" t="s">
-        <v>584</v>
+        <v>470</v>
       </c>
     </row>
     <row r="191" spans="11:17">
       <c r="K191" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q191" t="s">
-        <v>470</v>
+        <v>588</v>
       </c>
     </row>
     <row r="192" spans="11:17">
       <c r="K192" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Q192" t="s">
         <v>471</v>
@@ -5366,7 +5383,7 @@
     </row>
     <row r="193" spans="11:17">
       <c r="K193" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Q193" t="s">
         <v>472</v>
@@ -5374,7 +5391,7 @@
     </row>
     <row r="194" spans="11:17">
       <c r="K194" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q194" t="s">
         <v>473</v>
@@ -5382,7 +5399,7 @@
     </row>
     <row r="195" spans="11:17">
       <c r="K195" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Q195" t="s">
         <v>474</v>
@@ -5390,7 +5407,7 @@
     </row>
     <row r="196" spans="11:17">
       <c r="K196" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q196" t="s">
         <v>475</v>
@@ -5398,7 +5415,7 @@
     </row>
     <row r="197" spans="11:17">
       <c r="K197" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q197" t="s">
         <v>476</v>
@@ -5406,7 +5423,7 @@
     </row>
     <row r="198" spans="11:17">
       <c r="K198" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q198" t="s">
         <v>477</v>
@@ -5414,7 +5431,7 @@
     </row>
     <row r="199" spans="11:17">
       <c r="K199" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q199" t="s">
         <v>478</v>
@@ -5422,7 +5439,7 @@
     </row>
     <row r="200" spans="11:17">
       <c r="K200" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q200" t="s">
         <v>479</v>
@@ -5430,7 +5447,7 @@
     </row>
     <row r="201" spans="11:17">
       <c r="K201" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Q201" t="s">
         <v>480</v>
@@ -5438,7 +5455,7 @@
     </row>
     <row r="202" spans="11:17">
       <c r="K202" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Q202" t="s">
         <v>481</v>
@@ -5446,7 +5463,7 @@
     </row>
     <row r="203" spans="11:17">
       <c r="K203" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Q203" t="s">
         <v>482</v>
@@ -5454,7 +5471,7 @@
     </row>
     <row r="204" spans="11:17">
       <c r="K204" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Q204" t="s">
         <v>483</v>
@@ -5462,7 +5479,7 @@
     </row>
     <row r="205" spans="11:17">
       <c r="K205" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q205" t="s">
         <v>484</v>
@@ -5470,7 +5487,7 @@
     </row>
     <row r="206" spans="11:17">
       <c r="K206" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q206" t="s">
         <v>485</v>
@@ -5478,7 +5495,7 @@
     </row>
     <row r="207" spans="11:17">
       <c r="K207" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q207" t="s">
         <v>486</v>
@@ -5486,23 +5503,23 @@
     </row>
     <row r="208" spans="11:17">
       <c r="K208" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Q208" t="s">
-        <v>585</v>
+        <v>487</v>
       </c>
     </row>
     <row r="209" spans="11:17">
       <c r="K209" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q209" t="s">
-        <v>487</v>
+        <v>589</v>
       </c>
     </row>
     <row r="210" spans="11:17">
       <c r="K210" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q210" t="s">
         <v>488</v>
@@ -5510,586 +5527,611 @@
     </row>
     <row r="211" spans="11:17">
       <c r="K211" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q211" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="212" spans="11:17">
       <c r="K212" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q212" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="213" spans="11:17">
       <c r="K213" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Q213" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="214" spans="11:17">
       <c r="K214" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="Q214" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="215" spans="11:17">
       <c r="K215" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="Q215" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="216" spans="11:17">
       <c r="K216" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="Q216" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="217" spans="11:17">
       <c r="K217" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="Q217" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="218" spans="11:17">
       <c r="K218" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="Q218" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="219" spans="11:17">
       <c r="K219" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Q219" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="220" spans="11:17">
       <c r="K220" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Q220" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="221" spans="11:17">
       <c r="K221" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="Q221" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="222" spans="11:17">
       <c r="K222" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Q222" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="223" spans="11:17">
       <c r="K223" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q223" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="224" spans="11:17">
       <c r="K224" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Q224" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="225" spans="11:17">
       <c r="K225" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="Q225" t="s">
-        <v>586</v>
+        <v>504</v>
       </c>
     </row>
     <row r="226" spans="11:17">
       <c r="K226" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Q226" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="227" spans="11:17">
       <c r="K227" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Q227" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="228" spans="11:17">
       <c r="K228" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Q228" t="s">
-        <v>508</v>
+        <v>590</v>
       </c>
     </row>
     <row r="229" spans="11:17">
       <c r="K229" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Q229" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="230" spans="11:17">
       <c r="K230" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="Q230" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="231" spans="11:17">
       <c r="K231" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Q231" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="232" spans="11:17">
       <c r="K232" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Q232" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="233" spans="11:17">
       <c r="K233" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="Q233" t="s">
-        <v>587</v>
+        <v>511</v>
       </c>
     </row>
     <row r="234" spans="11:17">
       <c r="K234" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q234" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="235" spans="11:17">
       <c r="K235" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q235" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="236" spans="11:17">
       <c r="K236" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q236" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="237" spans="11:17">
       <c r="K237" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Q237" t="s">
-        <v>518</v>
+        <v>591</v>
       </c>
     </row>
     <row r="238" spans="11:17">
       <c r="K238" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="Q238" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="239" spans="11:17">
       <c r="K239" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Q239" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="240" spans="11:17">
       <c r="K240" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="Q240" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="241" spans="11:17">
       <c r="K241" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Q241" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="242" spans="11:17">
       <c r="K242" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Q242" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="243" spans="11:17">
       <c r="K243" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="Q243" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="244" spans="11:17">
       <c r="K244" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q244" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="245" spans="11:17">
       <c r="K245" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q245" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="246" spans="11:17">
       <c r="K246" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Q246" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="247" spans="11:17">
       <c r="K247" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Q247" t="s">
-        <v>588</v>
+        <v>525</v>
       </c>
     </row>
     <row r="248" spans="11:17">
       <c r="K248" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Q248" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="249" spans="11:17">
       <c r="K249" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Q249" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="250" spans="11:17">
       <c r="K250" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Q250" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
     </row>
     <row r="251" spans="11:17">
       <c r="K251" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="Q251" t="s">
-        <v>532</v>
+        <v>592</v>
       </c>
     </row>
     <row r="252" spans="11:17">
       <c r="K252" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Q252" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="253" spans="11:17">
       <c r="K253" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Q253" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="254" spans="11:17">
       <c r="K254" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q254" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="255" spans="11:17">
       <c r="K255" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Q255" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="256" spans="11:17">
       <c r="K256" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Q256" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="257" spans="11:17">
       <c r="K257" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Q257" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="258" spans="11:17">
       <c r="K258" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Q258" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
     </row>
     <row r="259" spans="11:17">
       <c r="K259" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q259" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="260" spans="11:17">
       <c r="K260" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Q260" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="261" spans="11:17">
       <c r="K261" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Q261" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="262" spans="11:17">
       <c r="K262" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Q262" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="263" spans="11:17">
       <c r="K263" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Q263" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="264" spans="11:17">
       <c r="K264" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Q264" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="265" spans="11:17">
       <c r="K265" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Q265" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="266" spans="11:17">
       <c r="K266" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Q266" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="267" spans="11:17">
       <c r="K267" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="Q267" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="268" spans="11:17">
       <c r="K268" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Q268" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="269" spans="11:17">
       <c r="K269" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Q269" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="270" spans="11:17">
       <c r="K270" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q270" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="271" spans="11:17">
       <c r="K271" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q271" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="272" spans="11:17">
       <c r="K272" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Q272" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="273" spans="11:17">
       <c r="K273" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Q273" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="274" spans="11:17">
       <c r="Q274" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="275" spans="11:17">
       <c r="Q275" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="276" spans="11:17">
       <c r="Q276" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="277" spans="11:17">
       <c r="Q277" t="s">
-        <v>589</v>
+        <v>555</v>
       </c>
     </row>
     <row r="278" spans="11:17">
       <c r="Q278" t="s">
-        <v>590</v>
+        <v>556</v>
       </c>
     </row>
     <row r="279" spans="11:17">
       <c r="Q279" t="s">
-        <v>591</v>
+        <v>557</v>
       </c>
     </row>
     <row r="280" spans="11:17">
       <c r="Q280" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
     </row>
     <row r="281" spans="11:17">
       <c r="Q281" t="s">
-        <v>593</v>
+        <v>559</v>
       </c>
     </row>
     <row r="282" spans="11:17">
       <c r="Q282" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="283" spans="11:17">
       <c r="Q283" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="284" spans="11:17">
       <c r="Q284" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="285" spans="11:17">
       <c r="Q285" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="286" spans="11:17">
       <c r="Q286" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="287" spans="11:17">
       <c r="Q287" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="288" spans="11:17">
       <c r="Q288" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="289" spans="17:17">
       <c r="Q289" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="290" spans="17:17">
+      <c r="Q290" t="s">
         <v>601</v>
+      </c>
+    </row>
+    <row r="291" spans="17:17">
+      <c r="Q291" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="292" spans="17:17">
+      <c r="Q292" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="293" spans="17:17">
+      <c r="Q293" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="294" spans="17:17">
+      <c r="Q294" t="s">
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000039/metadata_template_ERC000039.xlsx
+++ b/templates/ERC000039/metadata_template_ERC000039.xlsx
@@ -1770,7 +1770,7 @@
     <t>subject exposure duration</t>
   </si>
   <si>
-    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: year)</t>
+    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: day)</t>
   </si>
   <si>
     <t>Arctic Ocean</t>
